--- a/O Cubo.xlsx
+++ b/O Cubo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26DD90B6-952A-4C22-80FA-56A4B066BA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA74D2FE-3E19-438F-A4D4-0A3BE83BB114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="835" activeTab="2" xr2:uid="{CC72415A-D2E5-4D77-82BF-05A7B4384BC9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="835" activeTab="10" xr2:uid="{CC72415A-D2E5-4D77-82BF-05A7B4384BC9}"/>
   </bookViews>
   <sheets>
     <sheet name="COMPRAS" sheetId="19" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="76">
   <si>
     <t>Draw</t>
   </si>
@@ -280,6 +280,9 @@
   <si>
     <t>L Cemitério</t>
   </si>
+  <si>
+    <t>Blech, Loafing Pest</t>
+  </si>
 </sst>
 </file>
 
@@ -374,11 +377,11 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4032,17 +4035,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -4078,7 +4081,7 @@
       </c>
       <c r="B4"/>
       <c r="D4" s="3" t="str">
-        <f t="shared" ref="D4:D22" si="0">IF(B4=C4, "Sim", "Não")</f>
+        <f t="shared" ref="D4:D17" si="0">IF(B4=C4, "Sim", "Não")</f>
         <v>Sim</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -4520,17 +4523,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -4547,7 +4550,12 @@
       <c r="A3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B3"/>
+      <c r="B3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" t="s">
+        <v>75</v>
+      </c>
       <c r="D3" s="3" t="str">
         <f>IF(B3=C3, "Sim", "Não")</f>
         <v>Sim</v>
@@ -4566,7 +4574,7 @@
       </c>
       <c r="B4"/>
       <c r="D4" s="3" t="str">
-        <f t="shared" ref="D4:D22" si="0">IF(B4=C4, "Sim", "Não")</f>
+        <f t="shared" ref="D4:D17" si="0">IF(B4=C4, "Sim", "Não")</f>
         <v>Sim</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -5008,17 +5016,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -5054,7 +5062,7 @@
       </c>
       <c r="B4"/>
       <c r="D4" s="3" t="str">
-        <f t="shared" ref="D4:D22" si="0">IF(B4=C4, "Sim", "Não")</f>
+        <f t="shared" ref="D4:D17" si="0">IF(B4=C4, "Sim", "Não")</f>
         <v>Sim</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -5496,17 +5504,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -5542,7 +5550,7 @@
       </c>
       <c r="B4"/>
       <c r="D4" s="3" t="str">
-        <f t="shared" ref="D4:D22" si="0">IF(B4=C4, "Sim", "Não")</f>
+        <f t="shared" ref="D4:D17" si="0">IF(B4=C4, "Sim", "Não")</f>
         <v>Sim</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -5984,18 +5992,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -7062,18 +7070,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -8140,18 +8148,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -9218,18 +9226,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -10296,18 +10304,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -11374,18 +11382,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -11427,7 +11435,7 @@
       </c>
       <c r="B4"/>
       <c r="D4" s="3" t="str">
-        <f t="shared" ref="D4:D66" si="0">IF(B4=C4, "Sim", "Não")</f>
+        <f t="shared" ref="D4:D52" si="0">IF(B4=C4, "Sim", "Não")</f>
         <v>Sim</v>
       </c>
       <c r="E4" s="3" t="s">
@@ -13312,14 +13320,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -13358,7 +13366,7 @@
       </c>
       <c r="B4"/>
       <c r="D4" s="3" t="str">
-        <f t="shared" ref="D4:D22" si="0">IF(B4=C4, "Sim", "Não")</f>
+        <f t="shared" ref="D4:D17" si="0">IF(B4=C4, "Sim", "Não")</f>
         <v>Sim</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -13800,17 +13808,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -13846,7 +13854,7 @@
       </c>
       <c r="B4"/>
       <c r="D4" s="3" t="str">
-        <f t="shared" ref="D4:D22" si="0">IF(B4=C4, "Sim", "Não")</f>
+        <f t="shared" ref="D4:D17" si="0">IF(B4=C4, "Sim", "Não")</f>
         <v>Sim</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -14288,17 +14296,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -14334,7 +14342,7 @@
       </c>
       <c r="B4"/>
       <c r="D4" s="3" t="str">
-        <f t="shared" ref="D4:D22" si="0">IF(B4=C4, "Sim", "Não")</f>
+        <f t="shared" ref="D4:D17" si="0">IF(B4=C4, "Sim", "Não")</f>
         <v>Sim</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -14776,17 +14784,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -14822,7 +14830,7 @@
       </c>
       <c r="B4"/>
       <c r="D4" s="3" t="str">
-        <f t="shared" ref="D4:D22" si="0">IF(B4=C4, "Sim", "Não")</f>
+        <f t="shared" ref="D4:D17" si="0">IF(B4=C4, "Sim", "Não")</f>
         <v>Sim</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -15264,17 +15272,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -15310,7 +15318,7 @@
       </c>
       <c r="B4"/>
       <c r="D4" s="3" t="str">
-        <f t="shared" ref="D4:D22" si="0">IF(B4=C4, "Sim", "Não")</f>
+        <f t="shared" ref="D4:D17" si="0">IF(B4=C4, "Sim", "Não")</f>
         <v>Sim</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -15752,17 +15760,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -15798,7 +15806,7 @@
       </c>
       <c r="B4"/>
       <c r="D4" s="3" t="str">
-        <f t="shared" ref="D4:D22" si="0">IF(B4=C4, "Sim", "Não")</f>
+        <f t="shared" ref="D4:D17" si="0">IF(B4=C4, "Sim", "Não")</f>
         <v>Sim</v>
       </c>
       <c r="F4" s="4" t="s">
